--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271C5304-3FA0-4FF8-8C58-0751B1D05874}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C326A9F0-74BB-4B39-B7E1-13D2D6B2E73C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="624" windowWidth="20820" windowHeight="13056" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -531,6 +531,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
